--- a/outputs/validation_report.xlsx
+++ b/outputs/validation_report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H701"/>
+  <dimension ref="A1:I701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,10 +450,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Level_numeric</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Level_Way_A</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Level_Way_B</t>
         </is>
@@ -492,6 +497,9 @@
       <c r="H2" t="n">
         <v>3</v>
       </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +534,9 @@
       <c r="H3" t="n">
         <v>3</v>
       </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -560,6 +571,9 @@
       <c r="H4" t="n">
         <v>3</v>
       </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,6 +608,9 @@
       <c r="H5" t="n">
         <v>3</v>
       </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -628,6 +645,9 @@
       <c r="H6" t="n">
         <v>3</v>
       </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +682,9 @@
       <c r="H7" t="n">
         <v>3</v>
       </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -696,6 +719,9 @@
       <c r="H8" t="n">
         <v>3</v>
       </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -730,6 +756,9 @@
       <c r="H9" t="n">
         <v>2</v>
       </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -764,6 +793,9 @@
       <c r="H10" t="n">
         <v>2</v>
       </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,6 +830,9 @@
       <c r="H11" t="n">
         <v>4</v>
       </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -830,6 +865,9 @@
         <v>3</v>
       </c>
       <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -856,10 +894,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -894,6 +931,9 @@
       <c r="H14" t="n">
         <v>4</v>
       </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -928,6 +968,9 @@
       <c r="H15" t="n">
         <v>3</v>
       </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -962,6 +1005,9 @@
       <c r="H16" t="n">
         <v>3</v>
       </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -996,6 +1042,9 @@
       <c r="H17" t="n">
         <v>3</v>
       </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1079,9 @@
       <c r="H18" t="n">
         <v>3</v>
       </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1064,6 +1116,9 @@
       <c r="H19" t="n">
         <v>3</v>
       </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1098,6 +1153,9 @@
       <c r="H20" t="n">
         <v>2</v>
       </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1132,6 +1190,9 @@
       <c r="H21" t="n">
         <v>3</v>
       </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1166,6 +1227,9 @@
       <c r="H22" t="n">
         <v>2</v>
       </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1200,6 +1264,9 @@
       <c r="H23" t="n">
         <v>4</v>
       </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1234,6 +1301,9 @@
       <c r="H24" t="n">
         <v>3</v>
       </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1268,6 +1338,9 @@
       <c r="H25" t="n">
         <v>2</v>
       </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1302,6 +1375,9 @@
       <c r="H26" t="n">
         <v>3</v>
       </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1336,6 +1412,9 @@
       <c r="H27" t="n">
         <v>3</v>
       </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1370,6 +1449,9 @@
       <c r="H28" t="n">
         <v>3</v>
       </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1404,6 +1486,9 @@
       <c r="H29" t="n">
         <v>3</v>
       </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1438,6 +1523,9 @@
       <c r="H30" t="n">
         <v>2</v>
       </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1472,6 +1560,9 @@
       <c r="H31" t="n">
         <v>3</v>
       </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1506,6 +1597,9 @@
       <c r="H32" t="n">
         <v>3</v>
       </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1540,6 +1634,9 @@
       <c r="H33" t="n">
         <v>4</v>
       </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1574,6 +1671,9 @@
       <c r="H34" t="n">
         <v>3</v>
       </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1608,6 +1708,9 @@
       <c r="H35" t="n">
         <v>2</v>
       </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1642,6 +1745,9 @@
       <c r="H36" t="n">
         <v>3</v>
       </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1676,6 +1782,9 @@
       <c r="H37" t="n">
         <v>3</v>
       </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1708,6 +1817,9 @@
         <v>3</v>
       </c>
       <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1734,10 +1846,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1772,6 +1883,9 @@
       <c r="H40" t="n">
         <v>3</v>
       </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1806,6 +1920,9 @@
       <c r="H41" t="n">
         <v>4</v>
       </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1840,6 +1957,9 @@
       <c r="H42" t="n">
         <v>4</v>
       </c>
+      <c r="I42" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1874,6 +1994,9 @@
       <c r="H43" t="n">
         <v>4</v>
       </c>
+      <c r="I43" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1908,6 +2031,9 @@
       <c r="H44" t="n">
         <v>4</v>
       </c>
+      <c r="I44" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1942,6 +2068,9 @@
       <c r="H45" t="n">
         <v>4</v>
       </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1976,6 +2105,9 @@
       <c r="H46" t="n">
         <v>4</v>
       </c>
+      <c r="I46" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2010,6 +2142,9 @@
       <c r="H47" t="n">
         <v>4</v>
       </c>
+      <c r="I47" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2044,6 +2179,9 @@
       <c r="H48" t="n">
         <v>4</v>
       </c>
+      <c r="I48" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2078,6 +2216,9 @@
       <c r="H49" t="n">
         <v>4</v>
       </c>
+      <c r="I49" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2112,6 +2253,9 @@
       <c r="H50" t="n">
         <v>4</v>
       </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2146,6 +2290,9 @@
       <c r="H51" t="n">
         <v>4</v>
       </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2180,6 +2327,9 @@
       <c r="H52" t="n">
         <v>4</v>
       </c>
+      <c r="I52" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2214,6 +2364,9 @@
       <c r="H53" t="n">
         <v>3</v>
       </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2248,6 +2401,9 @@
       <c r="H54" t="n">
         <v>2</v>
       </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2282,6 +2438,9 @@
       <c r="H55" t="n">
         <v>4</v>
       </c>
+      <c r="I55" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2316,6 +2475,9 @@
       <c r="H56" t="n">
         <v>4</v>
       </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2348,6 +2510,9 @@
         <v>3</v>
       </c>
       <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2374,10 +2539,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2402,10 +2566,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2440,6 +2603,9 @@
       <c r="H60" t="n">
         <v>3</v>
       </c>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2474,6 +2640,9 @@
       <c r="H61" t="n">
         <v>4</v>
       </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2508,6 +2677,9 @@
       <c r="H62" t="n">
         <v>4</v>
       </c>
+      <c r="I62" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2542,6 +2714,9 @@
       <c r="H63" t="n">
         <v>3</v>
       </c>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2576,6 +2751,9 @@
       <c r="H64" t="n">
         <v>4</v>
       </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2610,6 +2788,9 @@
       <c r="H65" t="n">
         <v>3</v>
       </c>
+      <c r="I65" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2644,6 +2825,9 @@
       <c r="H66" t="n">
         <v>3</v>
       </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2678,6 +2862,9 @@
       <c r="H67" t="n">
         <v>3</v>
       </c>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2710,6 +2897,9 @@
         <v>3</v>
       </c>
       <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2736,10 +2926,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2764,10 +2953,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2792,10 +2980,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2820,10 +3007,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2848,10 +3034,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2876,10 +3061,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2912,6 +3096,9 @@
         <v>3</v>
       </c>
       <c r="H75" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2938,10 +3125,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2974,6 +3160,9 @@
         <v>2</v>
       </c>
       <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3000,10 +3189,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3038,6 +3226,9 @@
       <c r="H79" t="n">
         <v>3</v>
       </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3072,6 +3263,9 @@
       <c r="H80" t="n">
         <v>4</v>
       </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3106,6 +3300,9 @@
       <c r="H81" t="n">
         <v>4</v>
       </c>
+      <c r="I81" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3140,6 +3337,9 @@
       <c r="H82" t="n">
         <v>4</v>
       </c>
+      <c r="I82" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3174,6 +3374,9 @@
       <c r="H83" t="n">
         <v>3</v>
       </c>
+      <c r="I83" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3206,6 +3409,9 @@
         <v>3</v>
       </c>
       <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3232,10 +3438,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3260,10 +3465,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3298,6 +3502,9 @@
       <c r="H87" t="n">
         <v>4</v>
       </c>
+      <c r="I87" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3332,6 +3539,9 @@
       <c r="H88" t="n">
         <v>4</v>
       </c>
+      <c r="I88" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3366,6 +3576,9 @@
       <c r="H89" t="n">
         <v>4</v>
       </c>
+      <c r="I89" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3398,6 +3611,9 @@
         <v>3</v>
       </c>
       <c r="H90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3424,10 +3640,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3452,10 +3667,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3480,10 +3694,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3516,6 +3729,9 @@
         <v>4</v>
       </c>
       <c r="H94" t="n">
+        <v>4</v>
+      </c>
+      <c r="I94" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3542,10 +3758,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3570,10 +3785,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3608,6 +3822,9 @@
       <c r="H97" t="n">
         <v>3</v>
       </c>
+      <c r="I97" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3640,6 +3857,9 @@
         <v>3</v>
       </c>
       <c r="H98" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3666,10 +3886,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3704,6 +3923,9 @@
       <c r="H100" t="n">
         <v>3</v>
       </c>
+      <c r="I100" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3738,6 +3960,9 @@
       <c r="H101" t="n">
         <v>4</v>
       </c>
+      <c r="I101" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3770,6 +3995,9 @@
         <v>3</v>
       </c>
       <c r="H102" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3796,10 +4024,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3832,6 +4059,9 @@
         <v>3</v>
       </c>
       <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3858,10 +4088,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3896,6 +4125,9 @@
       <c r="H106" t="n">
         <v>4</v>
       </c>
+      <c r="I106" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3930,6 +4162,9 @@
       <c r="H107" t="n">
         <v>3</v>
       </c>
+      <c r="I107" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3964,6 +4199,9 @@
       <c r="H108" t="n">
         <v>3</v>
       </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3998,6 +4236,9 @@
       <c r="H109" t="n">
         <v>3</v>
       </c>
+      <c r="I109" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4032,6 +4273,9 @@
       <c r="H110" t="n">
         <v>4</v>
       </c>
+      <c r="I110" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4066,6 +4310,9 @@
       <c r="H111" t="n">
         <v>4</v>
       </c>
+      <c r="I111" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4100,6 +4347,9 @@
       <c r="H112" t="n">
         <v>3</v>
       </c>
+      <c r="I112" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4134,6 +4384,9 @@
       <c r="H113" t="n">
         <v>4</v>
       </c>
+      <c r="I113" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4168,6 +4421,9 @@
       <c r="H114" t="n">
         <v>4</v>
       </c>
+      <c r="I114" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4202,6 +4458,9 @@
       <c r="H115" t="n">
         <v>3</v>
       </c>
+      <c r="I115" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4236,6 +4495,9 @@
       <c r="H116" t="n">
         <v>3</v>
       </c>
+      <c r="I116" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4270,6 +4532,9 @@
       <c r="H117" t="n">
         <v>3</v>
       </c>
+      <c r="I117" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4304,6 +4569,9 @@
       <c r="H118" t="n">
         <v>4</v>
       </c>
+      <c r="I118" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4338,6 +4606,9 @@
       <c r="H119" t="n">
         <v>2</v>
       </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4372,6 +4643,9 @@
       <c r="H120" t="n">
         <v>3</v>
       </c>
+      <c r="I120" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4404,6 +4678,9 @@
         <v>3</v>
       </c>
       <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4430,10 +4707,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4466,6 +4742,9 @@
         <v>3</v>
       </c>
       <c r="H123" t="n">
+        <v>3</v>
+      </c>
+      <c r="I123" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4492,10 +4771,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4528,6 +4806,9 @@
         <v>2</v>
       </c>
       <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4554,10 +4835,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4592,6 +4872,9 @@
       <c r="H127" t="n">
         <v>2</v>
       </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4626,6 +4909,9 @@
       <c r="H128" t="n">
         <v>3</v>
       </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4660,6 +4946,9 @@
       <c r="H129" t="n">
         <v>3</v>
       </c>
+      <c r="I129" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4694,6 +4983,9 @@
       <c r="H130" t="n">
         <v>3</v>
       </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4726,6 +5018,9 @@
         <v>3</v>
       </c>
       <c r="H131" t="n">
+        <v>3</v>
+      </c>
+      <c r="I131" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4752,10 +5047,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4788,6 +5082,9 @@
         <v>2</v>
       </c>
       <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4814,10 +5111,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4842,10 +5138,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4870,10 +5165,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4898,10 +5192,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4926,10 +5219,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4964,6 +5256,9 @@
       <c r="H139" t="n">
         <v>3</v>
       </c>
+      <c r="I139" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4998,6 +5293,9 @@
       <c r="H140" t="n">
         <v>3</v>
       </c>
+      <c r="I140" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5032,6 +5330,9 @@
       <c r="H141" t="n">
         <v>3</v>
       </c>
+      <c r="I141" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5066,6 +5367,9 @@
       <c r="H142" t="n">
         <v>3</v>
       </c>
+      <c r="I142" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5100,6 +5404,9 @@
       <c r="H143" t="n">
         <v>3</v>
       </c>
+      <c r="I143" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5134,6 +5441,9 @@
       <c r="H144" t="n">
         <v>3</v>
       </c>
+      <c r="I144" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5168,6 +5478,9 @@
       <c r="H145" t="n">
         <v>4</v>
       </c>
+      <c r="I145" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5202,6 +5515,9 @@
       <c r="H146" t="n">
         <v>3</v>
       </c>
+      <c r="I146" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5236,6 +5552,9 @@
       <c r="H147" t="n">
         <v>4</v>
       </c>
+      <c r="I147" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5270,6 +5589,9 @@
       <c r="H148" t="n">
         <v>3</v>
       </c>
+      <c r="I148" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5304,6 +5626,9 @@
       <c r="H149" t="n">
         <v>4</v>
       </c>
+      <c r="I149" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5338,6 +5663,9 @@
       <c r="H150" t="n">
         <v>3</v>
       </c>
+      <c r="I150" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5372,6 +5700,9 @@
       <c r="H151" t="n">
         <v>4</v>
       </c>
+      <c r="I151" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5406,6 +5737,9 @@
       <c r="H152" t="n">
         <v>3</v>
       </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5440,6 +5774,9 @@
       <c r="H153" t="n">
         <v>3</v>
       </c>
+      <c r="I153" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5474,6 +5811,9 @@
       <c r="H154" t="n">
         <v>4</v>
       </c>
+      <c r="I154" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5508,6 +5848,9 @@
       <c r="H155" t="n">
         <v>4</v>
       </c>
+      <c r="I155" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5542,6 +5885,9 @@
       <c r="H156" t="n">
         <v>3</v>
       </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5576,6 +5922,9 @@
       <c r="H157" t="n">
         <v>4</v>
       </c>
+      <c r="I157" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5610,6 +5959,9 @@
       <c r="H158" t="n">
         <v>3</v>
       </c>
+      <c r="I158" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5644,6 +5996,9 @@
       <c r="H159" t="n">
         <v>3</v>
       </c>
+      <c r="I159" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5678,6 +6033,9 @@
       <c r="H160" t="n">
         <v>3</v>
       </c>
+      <c r="I160" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5712,6 +6070,9 @@
       <c r="H161" t="n">
         <v>3</v>
       </c>
+      <c r="I161" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5746,6 +6107,9 @@
       <c r="H162" t="n">
         <v>3</v>
       </c>
+      <c r="I162" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5780,6 +6144,9 @@
       <c r="H163" t="n">
         <v>3</v>
       </c>
+      <c r="I163" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5812,6 +6179,9 @@
         <v>3</v>
       </c>
       <c r="H164" t="n">
+        <v>3</v>
+      </c>
+      <c r="I164" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5838,10 +6208,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5876,6 +6245,9 @@
       <c r="H166" t="n">
         <v>4</v>
       </c>
+      <c r="I166" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5910,6 +6282,9 @@
       <c r="H167" t="n">
         <v>3</v>
       </c>
+      <c r="I167" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5944,6 +6319,9 @@
       <c r="H168" t="n">
         <v>3</v>
       </c>
+      <c r="I168" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5978,6 +6356,9 @@
       <c r="H169" t="n">
         <v>3</v>
       </c>
+      <c r="I169" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6012,6 +6393,9 @@
       <c r="H170" t="n">
         <v>2</v>
       </c>
+      <c r="I170" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6046,6 +6430,9 @@
       <c r="H171" t="n">
         <v>4</v>
       </c>
+      <c r="I171" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6080,6 +6467,9 @@
       <c r="H172" t="n">
         <v>4</v>
       </c>
+      <c r="I172" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6114,6 +6504,9 @@
       <c r="H173" t="n">
         <v>4</v>
       </c>
+      <c r="I173" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6148,6 +6541,9 @@
       <c r="H174" t="n">
         <v>4</v>
       </c>
+      <c r="I174" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6182,6 +6578,9 @@
       <c r="H175" t="n">
         <v>3</v>
       </c>
+      <c r="I175" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6216,6 +6615,9 @@
       <c r="H176" t="n">
         <v>4</v>
       </c>
+      <c r="I176" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6250,6 +6652,9 @@
       <c r="H177" t="n">
         <v>3</v>
       </c>
+      <c r="I177" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6282,6 +6687,9 @@
         <v>3</v>
       </c>
       <c r="H178" t="n">
+        <v>3</v>
+      </c>
+      <c r="I178" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6308,10 +6716,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6346,6 +6753,9 @@
       <c r="H180" t="n">
         <v>2</v>
       </c>
+      <c r="I180" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6380,6 +6790,9 @@
       <c r="H181" t="n">
         <v>3</v>
       </c>
+      <c r="I181" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6414,6 +6827,9 @@
       <c r="H182" t="n">
         <v>4</v>
       </c>
+      <c r="I182" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6448,6 +6864,9 @@
       <c r="H183" t="n">
         <v>4</v>
       </c>
+      <c r="I183" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6482,6 +6901,9 @@
       <c r="H184" t="n">
         <v>4</v>
       </c>
+      <c r="I184" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6516,6 +6938,9 @@
       <c r="H185" t="n">
         <v>4</v>
       </c>
+      <c r="I185" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6550,6 +6975,9 @@
       <c r="H186" t="n">
         <v>4</v>
       </c>
+      <c r="I186" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6584,6 +7012,9 @@
       <c r="H187" t="n">
         <v>4</v>
       </c>
+      <c r="I187" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6618,6 +7049,9 @@
       <c r="H188" t="n">
         <v>4</v>
       </c>
+      <c r="I188" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6652,6 +7086,9 @@
       <c r="H189" t="n">
         <v>3</v>
       </c>
+      <c r="I189" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6686,6 +7123,9 @@
       <c r="H190" t="n">
         <v>3</v>
       </c>
+      <c r="I190" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6720,6 +7160,9 @@
       <c r="H191" t="n">
         <v>4</v>
       </c>
+      <c r="I191" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6754,6 +7197,9 @@
       <c r="H192" t="n">
         <v>4</v>
       </c>
+      <c r="I192" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6788,6 +7234,9 @@
       <c r="H193" t="n">
         <v>3</v>
       </c>
+      <c r="I193" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6822,6 +7271,9 @@
       <c r="H194" t="n">
         <v>3</v>
       </c>
+      <c r="I194" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6856,6 +7308,9 @@
       <c r="H195" t="n">
         <v>4</v>
       </c>
+      <c r="I195" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6890,6 +7345,9 @@
       <c r="H196" t="n">
         <v>4</v>
       </c>
+      <c r="I196" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6924,6 +7382,9 @@
       <c r="H197" t="n">
         <v>3</v>
       </c>
+      <c r="I197" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6956,6 +7417,9 @@
         <v>3</v>
       </c>
       <c r="H198" t="n">
+        <v>3</v>
+      </c>
+      <c r="I198" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6982,10 +7446,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7020,6 +7483,9 @@
       <c r="H200" t="n">
         <v>4</v>
       </c>
+      <c r="I200" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7054,6 +7520,9 @@
       <c r="H201" t="n">
         <v>4</v>
       </c>
+      <c r="I201" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7086,6 +7555,9 @@
         <v>4</v>
       </c>
       <c r="H202" t="n">
+        <v>4</v>
+      </c>
+      <c r="I202" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7112,10 +7584,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G203" t="n">
-        <v>0</v>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7150,6 +7621,9 @@
       <c r="H204" t="n">
         <v>4</v>
       </c>
+      <c r="I204" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7184,6 +7658,9 @@
       <c r="H205" t="n">
         <v>4</v>
       </c>
+      <c r="I205" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7218,6 +7695,9 @@
       <c r="H206" t="n">
         <v>2</v>
       </c>
+      <c r="I206" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7252,6 +7732,9 @@
       <c r="H207" t="n">
         <v>4</v>
       </c>
+      <c r="I207" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7286,6 +7769,9 @@
       <c r="H208" t="n">
         <v>3</v>
       </c>
+      <c r="I208" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7318,6 +7804,9 @@
         <v>3</v>
       </c>
       <c r="H209" t="n">
+        <v>3</v>
+      </c>
+      <c r="I209" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7344,10 +7833,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7380,6 +7868,9 @@
         <v>3</v>
       </c>
       <c r="H211" t="n">
+        <v>3</v>
+      </c>
+      <c r="I211" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7406,10 +7897,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7434,10 +7924,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7462,10 +7951,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7500,6 +7988,9 @@
       <c r="H215" t="n">
         <v>4</v>
       </c>
+      <c r="I215" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7534,6 +8025,9 @@
       <c r="H216" t="n">
         <v>3</v>
       </c>
+      <c r="I216" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7566,6 +8060,9 @@
         <v>3</v>
       </c>
       <c r="H217" t="n">
+        <v>3</v>
+      </c>
+      <c r="I217" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7592,10 +8089,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G218" t="n">
-        <v>0</v>
-      </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7630,6 +8126,9 @@
       <c r="H219" t="n">
         <v>4</v>
       </c>
+      <c r="I219" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7664,6 +8163,9 @@
       <c r="H220" t="n">
         <v>4</v>
       </c>
+      <c r="I220" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7698,6 +8200,9 @@
       <c r="H221" t="n">
         <v>4</v>
       </c>
+      <c r="I221" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7732,6 +8237,9 @@
       <c r="H222" t="n">
         <v>4</v>
       </c>
+      <c r="I222" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7766,6 +8274,9 @@
       <c r="H223" t="n">
         <v>3</v>
       </c>
+      <c r="I223" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7800,6 +8311,9 @@
       <c r="H224" t="n">
         <v>3</v>
       </c>
+      <c r="I224" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7834,6 +8348,9 @@
       <c r="H225" t="n">
         <v>3</v>
       </c>
+      <c r="I225" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7868,6 +8385,9 @@
       <c r="H226" t="n">
         <v>3</v>
       </c>
+      <c r="I226" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7902,6 +8422,9 @@
       <c r="H227" t="n">
         <v>4</v>
       </c>
+      <c r="I227" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7936,6 +8459,9 @@
       <c r="H228" t="n">
         <v>4</v>
       </c>
+      <c r="I228" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7970,6 +8496,9 @@
       <c r="H229" t="n">
         <v>4</v>
       </c>
+      <c r="I229" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8004,6 +8533,9 @@
       <c r="H230" t="n">
         <v>4</v>
       </c>
+      <c r="I230" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8038,6 +8570,9 @@
       <c r="H231" t="n">
         <v>3</v>
       </c>
+      <c r="I231" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8072,6 +8607,9 @@
       <c r="H232" t="n">
         <v>3</v>
       </c>
+      <c r="I232" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8106,6 +8644,9 @@
       <c r="H233" t="n">
         <v>3</v>
       </c>
+      <c r="I233" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8138,6 +8679,9 @@
         <v>4</v>
       </c>
       <c r="H234" t="n">
+        <v>4</v>
+      </c>
+      <c r="I234" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8164,10 +8708,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8192,10 +8735,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G236" t="n">
-        <v>0</v>
-      </c>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8230,6 +8772,9 @@
       <c r="H237" t="n">
         <v>4</v>
       </c>
+      <c r="I237" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8262,6 +8807,9 @@
         <v>3</v>
       </c>
       <c r="H238" t="n">
+        <v>3</v>
+      </c>
+      <c r="I238" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8288,10 +8836,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8326,6 +8873,9 @@
       <c r="H240" t="n">
         <v>4</v>
       </c>
+      <c r="I240" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8360,6 +8910,9 @@
       <c r="H241" t="n">
         <v>4</v>
       </c>
+      <c r="I241" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8392,6 +8945,9 @@
         <v>3</v>
       </c>
       <c r="H242" t="n">
+        <v>3</v>
+      </c>
+      <c r="I242" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8418,10 +8974,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8456,6 +9011,9 @@
       <c r="H244" t="n">
         <v>3</v>
       </c>
+      <c r="I244" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8490,6 +9048,9 @@
       <c r="H245" t="n">
         <v>3</v>
       </c>
+      <c r="I245" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8524,6 +9085,9 @@
       <c r="H246" t="n">
         <v>4</v>
       </c>
+      <c r="I246" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8558,6 +9122,9 @@
       <c r="H247" t="n">
         <v>3</v>
       </c>
+      <c r="I247" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8592,6 +9159,9 @@
       <c r="H248" t="n">
         <v>3</v>
       </c>
+      <c r="I248" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8626,6 +9196,9 @@
       <c r="H249" t="n">
         <v>3</v>
       </c>
+      <c r="I249" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8660,6 +9233,9 @@
       <c r="H250" t="n">
         <v>3</v>
       </c>
+      <c r="I250" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8694,6 +9270,9 @@
       <c r="H251" t="n">
         <v>4</v>
       </c>
+      <c r="I251" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8728,6 +9307,9 @@
       <c r="H252" t="n">
         <v>3</v>
       </c>
+      <c r="I252" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8762,6 +9344,9 @@
       <c r="H253" t="n">
         <v>4</v>
       </c>
+      <c r="I253" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8796,6 +9381,9 @@
       <c r="H254" t="n">
         <v>3</v>
       </c>
+      <c r="I254" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8830,6 +9418,9 @@
       <c r="H255" t="n">
         <v>3</v>
       </c>
+      <c r="I255" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8864,6 +9455,9 @@
       <c r="H256" t="n">
         <v>4</v>
       </c>
+      <c r="I256" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8898,6 +9492,9 @@
       <c r="H257" t="n">
         <v>4</v>
       </c>
+      <c r="I257" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8932,6 +9529,9 @@
       <c r="H258" t="n">
         <v>4</v>
       </c>
+      <c r="I258" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8966,6 +9566,9 @@
       <c r="H259" t="n">
         <v>3</v>
       </c>
+      <c r="I259" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9000,6 +9603,9 @@
       <c r="H260" t="n">
         <v>3</v>
       </c>
+      <c r="I260" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9032,6 +9638,9 @@
         <v>3</v>
       </c>
       <c r="H261" t="n">
+        <v>3</v>
+      </c>
+      <c r="I261" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9058,10 +9667,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9094,6 +9702,9 @@
         <v>3</v>
       </c>
       <c r="H263" t="n">
+        <v>3</v>
+      </c>
+      <c r="I263" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9120,10 +9731,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9156,6 +9766,9 @@
         <v>3</v>
       </c>
       <c r="H265" t="n">
+        <v>3</v>
+      </c>
+      <c r="I265" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9182,10 +9795,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G266" t="n">
-        <v>0</v>
-      </c>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9220,6 +9832,9 @@
       <c r="H267" t="n">
         <v>4</v>
       </c>
+      <c r="I267" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9254,6 +9869,9 @@
       <c r="H268" t="n">
         <v>4</v>
       </c>
+      <c r="I268" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9288,6 +9906,9 @@
       <c r="H269" t="n">
         <v>4</v>
       </c>
+      <c r="I269" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9322,6 +9943,9 @@
       <c r="H270" t="n">
         <v>4</v>
       </c>
+      <c r="I270" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9356,6 +9980,9 @@
       <c r="H271" t="n">
         <v>3</v>
       </c>
+      <c r="I271" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9388,6 +10015,9 @@
         <v>3</v>
       </c>
       <c r="H272" t="n">
+        <v>3</v>
+      </c>
+      <c r="I272" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9414,10 +10044,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9452,6 +10081,9 @@
       <c r="H274" t="n">
         <v>3</v>
       </c>
+      <c r="I274" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9486,6 +10118,9 @@
       <c r="H275" t="n">
         <v>3</v>
       </c>
+      <c r="I275" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9520,6 +10155,9 @@
       <c r="H276" t="n">
         <v>3</v>
       </c>
+      <c r="I276" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9554,6 +10192,9 @@
       <c r="H277" t="n">
         <v>3</v>
       </c>
+      <c r="I277" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9588,6 +10229,9 @@
       <c r="H278" t="n">
         <v>3</v>
       </c>
+      <c r="I278" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9622,6 +10266,9 @@
       <c r="H279" t="n">
         <v>4</v>
       </c>
+      <c r="I279" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9656,6 +10303,9 @@
       <c r="H280" t="n">
         <v>4</v>
       </c>
+      <c r="I280" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9690,6 +10340,9 @@
       <c r="H281" t="n">
         <v>4</v>
       </c>
+      <c r="I281" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9724,6 +10377,9 @@
       <c r="H282" t="n">
         <v>4</v>
       </c>
+      <c r="I282" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9758,6 +10414,9 @@
       <c r="H283" t="n">
         <v>4</v>
       </c>
+      <c r="I283" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9792,6 +10451,9 @@
       <c r="H284" t="n">
         <v>4</v>
       </c>
+      <c r="I284" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9826,6 +10488,9 @@
       <c r="H285" t="n">
         <v>4</v>
       </c>
+      <c r="I285" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9860,6 +10525,9 @@
       <c r="H286" t="n">
         <v>3</v>
       </c>
+      <c r="I286" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9894,6 +10562,9 @@
       <c r="H287" t="n">
         <v>4</v>
       </c>
+      <c r="I287" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9928,6 +10599,9 @@
       <c r="H288" t="n">
         <v>3</v>
       </c>
+      <c r="I288" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9962,6 +10636,9 @@
       <c r="H289" t="n">
         <v>4</v>
       </c>
+      <c r="I289" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9996,6 +10673,9 @@
       <c r="H290" t="n">
         <v>3</v>
       </c>
+      <c r="I290" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10030,6 +10710,9 @@
       <c r="H291" t="n">
         <v>4</v>
       </c>
+      <c r="I291" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10064,6 +10747,9 @@
       <c r="H292" t="n">
         <v>4</v>
       </c>
+      <c r="I292" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10098,6 +10784,9 @@
       <c r="H293" t="n">
         <v>3</v>
       </c>
+      <c r="I293" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10132,6 +10821,9 @@
       <c r="H294" t="n">
         <v>4</v>
       </c>
+      <c r="I294" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10166,6 +10858,9 @@
       <c r="H295" t="n">
         <v>4</v>
       </c>
+      <c r="I295" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10200,6 +10895,9 @@
       <c r="H296" t="n">
         <v>4</v>
       </c>
+      <c r="I296" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10234,6 +10932,9 @@
       <c r="H297" t="n">
         <v>3</v>
       </c>
+      <c r="I297" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10268,6 +10969,9 @@
       <c r="H298" t="n">
         <v>3</v>
       </c>
+      <c r="I298" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10302,6 +11006,9 @@
       <c r="H299" t="n">
         <v>4</v>
       </c>
+      <c r="I299" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10336,6 +11043,9 @@
       <c r="H300" t="n">
         <v>3</v>
       </c>
+      <c r="I300" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10370,6 +11080,9 @@
       <c r="H301" t="n">
         <v>4</v>
       </c>
+      <c r="I301" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10404,6 +11117,9 @@
       <c r="H302" t="n">
         <v>4</v>
       </c>
+      <c r="I302" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10438,6 +11154,9 @@
       <c r="H303" t="n">
         <v>3</v>
       </c>
+      <c r="I303" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10472,6 +11191,9 @@
       <c r="H304" t="n">
         <v>3</v>
       </c>
+      <c r="I304" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10506,6 +11228,9 @@
       <c r="H305" t="n">
         <v>3</v>
       </c>
+      <c r="I305" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10540,6 +11265,9 @@
       <c r="H306" t="n">
         <v>4</v>
       </c>
+      <c r="I306" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10574,6 +11302,9 @@
       <c r="H307" t="n">
         <v>4</v>
       </c>
+      <c r="I307" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10606,6 +11337,9 @@
         <v>4</v>
       </c>
       <c r="H308" t="n">
+        <v>4</v>
+      </c>
+      <c r="I308" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10632,10 +11366,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G309" t="n">
-        <v>0</v>
-      </c>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10670,6 +11403,9 @@
       <c r="H310" t="n">
         <v>4</v>
       </c>
+      <c r="I310" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10702,6 +11438,9 @@
         <v>4</v>
       </c>
       <c r="H311" t="n">
+        <v>4</v>
+      </c>
+      <c r="I311" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10728,10 +11467,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G312" t="n">
-        <v>0</v>
-      </c>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10766,6 +11504,9 @@
       <c r="H313" t="n">
         <v>4</v>
       </c>
+      <c r="I313" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10800,6 +11541,9 @@
       <c r="H314" t="n">
         <v>4</v>
       </c>
+      <c r="I314" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10834,6 +11578,9 @@
       <c r="H315" t="n">
         <v>3</v>
       </c>
+      <c r="I315" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10866,6 +11613,9 @@
         <v>4</v>
       </c>
       <c r="H316" t="n">
+        <v>4</v>
+      </c>
+      <c r="I316" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10892,10 +11642,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
+      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10930,6 +11679,9 @@
       <c r="H318" t="n">
         <v>5</v>
       </c>
+      <c r="I318" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10964,6 +11716,9 @@
       <c r="H319" t="n">
         <v>3</v>
       </c>
+      <c r="I319" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10998,6 +11753,9 @@
       <c r="H320" t="n">
         <v>4</v>
       </c>
+      <c r="I320" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11032,6 +11790,9 @@
       <c r="H321" t="n">
         <v>4</v>
       </c>
+      <c r="I321" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11066,6 +11827,9 @@
       <c r="H322" t="n">
         <v>4</v>
       </c>
+      <c r="I322" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11100,6 +11864,9 @@
       <c r="H323" t="n">
         <v>4</v>
       </c>
+      <c r="I323" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11134,6 +11901,9 @@
       <c r="H324" t="n">
         <v>4</v>
       </c>
+      <c r="I324" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11168,6 +11938,9 @@
       <c r="H325" t="n">
         <v>4</v>
       </c>
+      <c r="I325" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11202,6 +11975,9 @@
       <c r="H326" t="n">
         <v>4</v>
       </c>
+      <c r="I326" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11236,6 +12012,9 @@
       <c r="H327" t="n">
         <v>4</v>
       </c>
+      <c r="I327" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11270,6 +12049,9 @@
       <c r="H328" t="n">
         <v>4</v>
       </c>
+      <c r="I328" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11304,6 +12086,9 @@
       <c r="H329" t="n">
         <v>4</v>
       </c>
+      <c r="I329" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11336,6 +12121,9 @@
         <v>4</v>
       </c>
       <c r="H330" t="n">
+        <v>4</v>
+      </c>
+      <c r="I330" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11362,10 +12150,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G331" t="n">
-        <v>0</v>
-      </c>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11400,6 +12187,9 @@
       <c r="H332" t="n">
         <v>4</v>
       </c>
+      <c r="I332" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11432,6 +12222,9 @@
         <v>4</v>
       </c>
       <c r="H333" t="n">
+        <v>4</v>
+      </c>
+      <c r="I333" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11458,10 +12251,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G334" t="n">
-        <v>0</v>
-      </c>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11496,6 +12288,9 @@
       <c r="H335" t="n">
         <v>4</v>
       </c>
+      <c r="I335" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11530,6 +12325,9 @@
       <c r="H336" t="n">
         <v>4</v>
       </c>
+      <c r="I336" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11562,6 +12360,9 @@
         <v>4</v>
       </c>
       <c r="H337" t="n">
+        <v>4</v>
+      </c>
+      <c r="I337" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11588,10 +12389,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G338" t="n">
-        <v>0</v>
-      </c>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11626,6 +12426,9 @@
       <c r="H339" t="n">
         <v>4</v>
       </c>
+      <c r="I339" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11660,6 +12463,9 @@
       <c r="H340" t="n">
         <v>4</v>
       </c>
+      <c r="I340" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11694,6 +12500,9 @@
       <c r="H341" t="n">
         <v>4</v>
       </c>
+      <c r="I341" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11728,6 +12537,9 @@
       <c r="H342" t="n">
         <v>4</v>
       </c>
+      <c r="I342" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11762,6 +12574,9 @@
       <c r="H343" t="n">
         <v>5</v>
       </c>
+      <c r="I343" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11796,6 +12611,9 @@
       <c r="H344" t="n">
         <v>5</v>
       </c>
+      <c r="I344" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11830,6 +12648,9 @@
       <c r="H345" t="n">
         <v>5</v>
       </c>
+      <c r="I345" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11864,6 +12685,9 @@
       <c r="H346" t="n">
         <v>4</v>
       </c>
+      <c r="I346" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11898,6 +12722,9 @@
       <c r="H347" t="n">
         <v>5</v>
       </c>
+      <c r="I347" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11932,6 +12759,9 @@
       <c r="H348" t="n">
         <v>4</v>
       </c>
+      <c r="I348" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11966,6 +12796,9 @@
       <c r="H349" t="n">
         <v>3</v>
       </c>
+      <c r="I349" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12000,6 +12833,9 @@
       <c r="H350" t="n">
         <v>3</v>
       </c>
+      <c r="I350" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12032,6 +12868,9 @@
         <v>3</v>
       </c>
       <c r="H351" t="n">
+        <v>3</v>
+      </c>
+      <c r="I351" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12058,10 +12897,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G352" t="n">
-        <v>0</v>
-      </c>
+      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12086,10 +12924,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G353" t="n">
-        <v>0</v>
-      </c>
+      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12124,6 +12961,9 @@
       <c r="H354" t="n">
         <v>4</v>
       </c>
+      <c r="I354" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12156,6 +12996,9 @@
         <v>4</v>
       </c>
       <c r="H355" t="n">
+        <v>4</v>
+      </c>
+      <c r="I355" t="n">
         <v>4</v>
       </c>
     </row>
@@ -12182,10 +13025,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G356" t="n">
-        <v>0</v>
-      </c>
+      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12218,6 +13060,9 @@
         <v>4</v>
       </c>
       <c r="H357" t="n">
+        <v>4</v>
+      </c>
+      <c r="I357" t="n">
         <v>4</v>
       </c>
     </row>
@@ -12244,10 +13089,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G358" t="n">
-        <v>0</v>
-      </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12282,6 +13126,9 @@
       <c r="H359" t="n">
         <v>5</v>
       </c>
+      <c r="I359" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12316,6 +13163,9 @@
       <c r="H360" t="n">
         <v>4</v>
       </c>
+      <c r="I360" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12350,6 +13200,9 @@
       <c r="H361" t="n">
         <v>4</v>
       </c>
+      <c r="I361" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12384,6 +13237,9 @@
       <c r="H362" t="n">
         <v>4</v>
       </c>
+      <c r="I362" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12418,6 +13274,9 @@
       <c r="H363" t="n">
         <v>4</v>
       </c>
+      <c r="I363" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12452,6 +13311,9 @@
       <c r="H364" t="n">
         <v>4</v>
       </c>
+      <c r="I364" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12486,6 +13348,9 @@
       <c r="H365" t="n">
         <v>3</v>
       </c>
+      <c r="I365" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12520,6 +13385,9 @@
       <c r="H366" t="n">
         <v>3</v>
       </c>
+      <c r="I366" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12554,6 +13422,9 @@
       <c r="H367" t="n">
         <v>4</v>
       </c>
+      <c r="I367" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12588,6 +13459,9 @@
       <c r="H368" t="n">
         <v>5</v>
       </c>
+      <c r="I368" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12622,6 +13496,9 @@
       <c r="H369" t="n">
         <v>5</v>
       </c>
+      <c r="I369" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12656,6 +13533,9 @@
       <c r="H370" t="n">
         <v>3</v>
       </c>
+      <c r="I370" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12688,6 +13568,9 @@
         <v>3</v>
       </c>
       <c r="H371" t="n">
+        <v>3</v>
+      </c>
+      <c r="I371" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12714,10 +13597,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G372" t="n">
-        <v>0</v>
-      </c>
+      <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12752,6 +13634,9 @@
       <c r="H373" t="n">
         <v>4</v>
       </c>
+      <c r="I373" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12784,6 +13669,9 @@
         <v>4</v>
       </c>
       <c r="H374" t="n">
+        <v>4</v>
+      </c>
+      <c r="I374" t="n">
         <v>4</v>
       </c>
     </row>
@@ -12810,10 +13698,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G375" t="n">
-        <v>0</v>
-      </c>
+      <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12838,10 +13725,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G376" t="n">
-        <v>0</v>
-      </c>
+      <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12876,6 +13762,9 @@
       <c r="H377" t="n">
         <v>4</v>
       </c>
+      <c r="I377" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12908,6 +13797,9 @@
         <v>4</v>
       </c>
       <c r="H378" t="n">
+        <v>4</v>
+      </c>
+      <c r="I378" t="n">
         <v>4</v>
       </c>
     </row>
@@ -12934,10 +13826,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G379" t="n">
-        <v>0</v>
-      </c>
+      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12972,6 +13863,9 @@
       <c r="H380" t="n">
         <v>5</v>
       </c>
+      <c r="I380" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13006,6 +13900,9 @@
       <c r="H381" t="n">
         <v>4</v>
       </c>
+      <c r="I381" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13040,6 +13937,9 @@
       <c r="H382" t="n">
         <v>4</v>
       </c>
+      <c r="I382" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13074,6 +13974,9 @@
       <c r="H383" t="n">
         <v>3</v>
       </c>
+      <c r="I383" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13106,6 +14009,9 @@
         <v>4</v>
       </c>
       <c r="H384" t="n">
+        <v>4</v>
+      </c>
+      <c r="I384" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13132,10 +14038,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G385" t="n">
-        <v>0</v>
-      </c>
+      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13168,6 +14073,9 @@
         <v>3</v>
       </c>
       <c r="H386" t="n">
+        <v>3</v>
+      </c>
+      <c r="I386" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13194,10 +14102,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G387" t="n">
-        <v>0</v>
-      </c>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13232,6 +14139,9 @@
       <c r="H388" t="n">
         <v>3</v>
       </c>
+      <c r="I388" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13266,6 +14176,9 @@
       <c r="H389" t="n">
         <v>3</v>
       </c>
+      <c r="I389" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13300,6 +14213,9 @@
       <c r="H390" t="n">
         <v>3</v>
       </c>
+      <c r="I390" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13334,6 +14250,9 @@
       <c r="H391" t="n">
         <v>4</v>
       </c>
+      <c r="I391" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13368,6 +14287,9 @@
       <c r="H392" t="n">
         <v>3</v>
       </c>
+      <c r="I392" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13402,6 +14324,9 @@
       <c r="H393" t="n">
         <v>3</v>
       </c>
+      <c r="I393" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13436,6 +14361,9 @@
       <c r="H394" t="n">
         <v>3</v>
       </c>
+      <c r="I394" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13470,6 +14398,9 @@
       <c r="H395" t="n">
         <v>4</v>
       </c>
+      <c r="I395" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13504,6 +14435,9 @@
       <c r="H396" t="n">
         <v>4</v>
       </c>
+      <c r="I396" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13538,6 +14472,9 @@
       <c r="H397" t="n">
         <v>4</v>
       </c>
+      <c r="I397" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13570,6 +14507,9 @@
         <v>4</v>
       </c>
       <c r="H398" t="n">
+        <v>4</v>
+      </c>
+      <c r="I398" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13596,10 +14536,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G399" t="n">
-        <v>0</v>
-      </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13632,6 +14571,9 @@
         <v>3</v>
       </c>
       <c r="H400" t="n">
+        <v>3</v>
+      </c>
+      <c r="I400" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13658,10 +14600,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G401" t="n">
-        <v>0</v>
-      </c>
+      <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13686,10 +14627,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G402" t="n">
-        <v>0</v>
-      </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -13714,10 +14654,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G403" t="n">
-        <v>0</v>
-      </c>
+      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13742,10 +14681,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G404" t="n">
-        <v>0</v>
-      </c>
+      <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -13780,6 +14718,9 @@
       <c r="H405" t="n">
         <v>3</v>
       </c>
+      <c r="I405" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -13814,6 +14755,9 @@
       <c r="H406" t="n">
         <v>3</v>
       </c>
+      <c r="I406" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -13848,6 +14792,9 @@
       <c r="H407" t="n">
         <v>4</v>
       </c>
+      <c r="I407" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -13882,6 +14829,9 @@
       <c r="H408" t="n">
         <v>3</v>
       </c>
+      <c r="I408" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13916,6 +14866,9 @@
       <c r="H409" t="n">
         <v>4</v>
       </c>
+      <c r="I409" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -13950,6 +14903,9 @@
       <c r="H410" t="n">
         <v>3</v>
       </c>
+      <c r="I410" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -13982,6 +14938,9 @@
         <v>3</v>
       </c>
       <c r="H411" t="n">
+        <v>3</v>
+      </c>
+      <c r="I411" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14008,10 +14967,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G412" t="n">
-        <v>0</v>
-      </c>
+      <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14046,6 +15004,9 @@
       <c r="H413" t="n">
         <v>4</v>
       </c>
+      <c r="I413" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14078,6 +15039,9 @@
         <v>3</v>
       </c>
       <c r="H414" t="n">
+        <v>3</v>
+      </c>
+      <c r="I414" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14104,10 +15068,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G415" t="n">
-        <v>0</v>
-      </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14142,6 +15105,9 @@
       <c r="H416" t="n">
         <v>4</v>
       </c>
+      <c r="I416" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14174,6 +15140,9 @@
         <v>3</v>
       </c>
       <c r="H417" t="n">
+        <v>3</v>
+      </c>
+      <c r="I417" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14200,10 +15169,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G418" t="n">
-        <v>0</v>
-      </c>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14238,6 +15206,9 @@
       <c r="H419" t="n">
         <v>4</v>
       </c>
+      <c r="I419" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14272,6 +15243,9 @@
       <c r="H420" t="n">
         <v>4</v>
       </c>
+      <c r="I420" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14306,6 +15280,9 @@
       <c r="H421" t="n">
         <v>4</v>
       </c>
+      <c r="I421" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14338,6 +15315,9 @@
         <v>2</v>
       </c>
       <c r="H422" t="n">
+        <v>2</v>
+      </c>
+      <c r="I422" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14364,10 +15344,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G423" t="n">
-        <v>0</v>
-      </c>
+      <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14402,6 +15381,9 @@
       <c r="H424" t="n">
         <v>3</v>
       </c>
+      <c r="I424" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14436,6 +15418,9 @@
       <c r="H425" t="n">
         <v>3</v>
       </c>
+      <c r="I425" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -14470,6 +15455,9 @@
       <c r="H426" t="n">
         <v>3</v>
       </c>
+      <c r="I426" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -14504,6 +15492,9 @@
       <c r="H427" t="n">
         <v>4</v>
       </c>
+      <c r="I427" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -14536,6 +15527,9 @@
         <v>2</v>
       </c>
       <c r="H428" t="n">
+        <v>2</v>
+      </c>
+      <c r="I428" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14562,10 +15556,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G429" t="n">
-        <v>0</v>
-      </c>
+      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -14600,6 +15593,9 @@
       <c r="H430" t="n">
         <v>2</v>
       </c>
+      <c r="I430" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -14634,6 +15630,9 @@
       <c r="H431" t="n">
         <v>4</v>
       </c>
+      <c r="I431" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -14668,6 +15667,9 @@
       <c r="H432" t="n">
         <v>3</v>
       </c>
+      <c r="I432" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -14702,6 +15704,9 @@
       <c r="H433" t="n">
         <v>3</v>
       </c>
+      <c r="I433" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -14736,6 +15741,9 @@
       <c r="H434" t="n">
         <v>3</v>
       </c>
+      <c r="I434" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -14770,6 +15778,9 @@
       <c r="H435" t="n">
         <v>3</v>
       </c>
+      <c r="I435" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -14804,6 +15815,9 @@
       <c r="H436" t="n">
         <v>2</v>
       </c>
+      <c r="I436" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -14838,6 +15852,9 @@
       <c r="H437" t="n">
         <v>3</v>
       </c>
+      <c r="I437" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -14870,6 +15887,9 @@
         <v>2</v>
       </c>
       <c r="H438" t="n">
+        <v>2</v>
+      </c>
+      <c r="I438" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14896,10 +15916,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G439" t="n">
-        <v>0</v>
-      </c>
+      <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -14924,10 +15943,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G440" t="n">
-        <v>0</v>
-      </c>
+      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -14962,6 +15980,9 @@
       <c r="H441" t="n">
         <v>4</v>
       </c>
+      <c r="I441" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -14996,6 +16017,9 @@
       <c r="H442" t="n">
         <v>3</v>
       </c>
+      <c r="I442" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15030,6 +16054,9 @@
       <c r="H443" t="n">
         <v>4</v>
       </c>
+      <c r="I443" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15062,6 +16089,9 @@
         <v>3</v>
       </c>
       <c r="H444" t="n">
+        <v>3</v>
+      </c>
+      <c r="I444" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15088,10 +16118,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G445" t="n">
-        <v>0</v>
-      </c>
+      <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15126,6 +16155,9 @@
       <c r="H446" t="n">
         <v>3</v>
       </c>
+      <c r="I446" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15158,6 +16190,9 @@
         <v>2</v>
       </c>
       <c r="H447" t="n">
+        <v>2</v>
+      </c>
+      <c r="I447" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15184,10 +16219,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G448" t="n">
-        <v>0</v>
-      </c>
+      <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15222,6 +16256,9 @@
       <c r="H449" t="n">
         <v>2</v>
       </c>
+      <c r="I449" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15256,6 +16293,9 @@
       <c r="H450" t="n">
         <v>2</v>
       </c>
+      <c r="I450" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15290,6 +16330,9 @@
       <c r="H451" t="n">
         <v>4</v>
       </c>
+      <c r="I451" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15324,6 +16367,9 @@
       <c r="H452" t="n">
         <v>3</v>
       </c>
+      <c r="I452" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15358,6 +16404,9 @@
       <c r="H453" t="n">
         <v>4</v>
       </c>
+      <c r="I453" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15392,6 +16441,9 @@
       <c r="H454" t="n">
         <v>4</v>
       </c>
+      <c r="I454" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15424,6 +16476,9 @@
         <v>3</v>
       </c>
       <c r="H455" t="n">
+        <v>3</v>
+      </c>
+      <c r="I455" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15450,10 +16505,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G456" t="n">
-        <v>0</v>
-      </c>
+      <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -15488,6 +16542,9 @@
       <c r="H457" t="n">
         <v>3</v>
       </c>
+      <c r="I457" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -15520,6 +16577,9 @@
         <v>3</v>
       </c>
       <c r="H458" t="n">
+        <v>3</v>
+      </c>
+      <c r="I458" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15546,10 +16606,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G459" t="n">
-        <v>0</v>
-      </c>
+      <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -15584,6 +16643,9 @@
       <c r="H460" t="n">
         <v>3</v>
       </c>
+      <c r="I460" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -15618,6 +16680,9 @@
       <c r="H461" t="n">
         <v>3</v>
       </c>
+      <c r="I461" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -15652,6 +16717,9 @@
       <c r="H462" t="n">
         <v>4</v>
       </c>
+      <c r="I462" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -15686,6 +16754,9 @@
       <c r="H463" t="n">
         <v>4</v>
       </c>
+      <c r="I463" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -15720,6 +16791,9 @@
       <c r="H464" t="n">
         <v>3</v>
       </c>
+      <c r="I464" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -15754,6 +16828,9 @@
       <c r="H465" t="n">
         <v>4</v>
       </c>
+      <c r="I465" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -15788,6 +16865,9 @@
       <c r="H466" t="n">
         <v>4</v>
       </c>
+      <c r="I466" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -15822,6 +16902,9 @@
       <c r="H467" t="n">
         <v>4</v>
       </c>
+      <c r="I467" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -15856,6 +16939,9 @@
       <c r="H468" t="n">
         <v>4</v>
       </c>
+      <c r="I468" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -15890,6 +16976,9 @@
       <c r="H469" t="n">
         <v>3</v>
       </c>
+      <c r="I469" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -15924,6 +17013,9 @@
       <c r="H470" t="n">
         <v>2</v>
       </c>
+      <c r="I470" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -15958,6 +17050,9 @@
       <c r="H471" t="n">
         <v>3</v>
       </c>
+      <c r="I471" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -15992,6 +17087,9 @@
       <c r="H472" t="n">
         <v>4</v>
       </c>
+      <c r="I472" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16026,6 +17124,9 @@
       <c r="H473" t="n">
         <v>2</v>
       </c>
+      <c r="I473" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16060,6 +17161,9 @@
       <c r="H474" t="n">
         <v>3</v>
       </c>
+      <c r="I474" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16094,6 +17198,9 @@
       <c r="H475" t="n">
         <v>4</v>
       </c>
+      <c r="I475" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16126,6 +17233,9 @@
         <v>3</v>
       </c>
       <c r="H476" t="n">
+        <v>3</v>
+      </c>
+      <c r="I476" t="n">
         <v>3</v>
       </c>
     </row>
@@ -16152,10 +17262,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G477" t="n">
-        <v>0</v>
-      </c>
+      <c r="G477" t="inlineStr"/>
       <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16180,10 +17289,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G478" t="n">
-        <v>0</v>
-      </c>
+      <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16208,10 +17316,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G479" t="n">
-        <v>0</v>
-      </c>
+      <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16246,6 +17353,9 @@
       <c r="H480" t="n">
         <v>2</v>
       </c>
+      <c r="I480" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16280,6 +17390,9 @@
       <c r="H481" t="n">
         <v>2</v>
       </c>
+      <c r="I481" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -16312,6 +17425,9 @@
         <v>3</v>
       </c>
       <c r="H482" t="n">
+        <v>3</v>
+      </c>
+      <c r="I482" t="n">
         <v>3</v>
       </c>
     </row>
@@ -16338,10 +17454,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G483" t="n">
-        <v>0</v>
-      </c>
+      <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -16376,6 +17491,9 @@
       <c r="H484" t="n">
         <v>3</v>
       </c>
+      <c r="I484" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -16408,6 +17526,9 @@
         <v>4</v>
       </c>
       <c r="H485" t="n">
+        <v>4</v>
+      </c>
+      <c r="I485" t="n">
         <v>4</v>
       </c>
     </row>
@@ -16434,10 +17555,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G486" t="n">
-        <v>0</v>
-      </c>
+      <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -16472,6 +17592,9 @@
       <c r="H487" t="n">
         <v>3</v>
       </c>
+      <c r="I487" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -16504,6 +17627,9 @@
         <v>3</v>
       </c>
       <c r="H488" t="n">
+        <v>3</v>
+      </c>
+      <c r="I488" t="n">
         <v>3</v>
       </c>
     </row>
@@ -16530,10 +17656,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G489" t="n">
-        <v>0</v>
-      </c>
+      <c r="G489" t="inlineStr"/>
       <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -16558,10 +17683,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G490" t="n">
-        <v>0</v>
-      </c>
+      <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -16586,10 +17710,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G491" t="n">
-        <v>0</v>
-      </c>
+      <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -16614,10 +17737,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G492" t="n">
-        <v>0</v>
-      </c>
+      <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -16642,10 +17764,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G493" t="n">
-        <v>0</v>
-      </c>
+      <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -16670,10 +17791,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G494" t="n">
-        <v>0</v>
-      </c>
+      <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -16706,6 +17826,9 @@
         <v>3</v>
       </c>
       <c r="H495" t="n">
+        <v>3</v>
+      </c>
+      <c r="I495" t="n">
         <v>3</v>
       </c>
     </row>
@@ -16732,10 +17855,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G496" t="n">
-        <v>0</v>
-      </c>
+      <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -16768,6 +17890,9 @@
         <v>2</v>
       </c>
       <c r="H497" t="n">
+        <v>2</v>
+      </c>
+      <c r="I497" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16794,10 +17919,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G498" t="n">
-        <v>0</v>
-      </c>
+      <c r="G498" t="inlineStr"/>
       <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -16832,6 +17956,9 @@
       <c r="H499" t="n">
         <v>3</v>
       </c>
+      <c r="I499" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -16866,6 +17993,9 @@
       <c r="H500" t="n">
         <v>3</v>
       </c>
+      <c r="I500" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -16900,6 +18030,9 @@
       <c r="H501" t="n">
         <v>4</v>
       </c>
+      <c r="I501" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -16934,6 +18067,9 @@
       <c r="H502" t="n">
         <v>4</v>
       </c>
+      <c r="I502" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -16966,6 +18102,9 @@
         <v>3</v>
       </c>
       <c r="H503" t="n">
+        <v>3</v>
+      </c>
+      <c r="I503" t="n">
         <v>3</v>
       </c>
     </row>
@@ -16992,10 +18131,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G504" t="n">
-        <v>0</v>
-      </c>
+      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17030,6 +18168,9 @@
       <c r="H505" t="n">
         <v>2</v>
       </c>
+      <c r="I505" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -17064,6 +18205,9 @@
       <c r="H506" t="n">
         <v>2</v>
       </c>
+      <c r="I506" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -17098,6 +18242,9 @@
       <c r="H507" t="n">
         <v>3</v>
       </c>
+      <c r="I507" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -17132,6 +18279,9 @@
       <c r="H508" t="n">
         <v>4</v>
       </c>
+      <c r="I508" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -17164,6 +18314,9 @@
         <v>4</v>
       </c>
       <c r="H509" t="n">
+        <v>4</v>
+      </c>
+      <c r="I509" t="n">
         <v>4</v>
       </c>
     </row>
@@ -17190,10 +18343,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G510" t="n">
-        <v>0</v>
-      </c>
+      <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -17218,10 +18370,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G511" t="n">
-        <v>0</v>
-      </c>
+      <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -17246,10 +18397,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G512" t="n">
-        <v>0</v>
-      </c>
+      <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -17274,10 +18424,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G513" t="n">
-        <v>0</v>
-      </c>
+      <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -17310,6 +18459,9 @@
         <v>3</v>
       </c>
       <c r="H514" t="n">
+        <v>3</v>
+      </c>
+      <c r="I514" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17336,10 +18488,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G515" t="n">
-        <v>0</v>
-      </c>
+      <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -17374,6 +18525,9 @@
       <c r="H516" t="n">
         <v>2</v>
       </c>
+      <c r="I516" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -17408,6 +18562,9 @@
       <c r="H517" t="n">
         <v>3</v>
       </c>
+      <c r="I517" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -17440,6 +18597,9 @@
         <v>2</v>
       </c>
       <c r="H518" t="n">
+        <v>2</v>
+      </c>
+      <c r="I518" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17466,10 +18626,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G519" t="n">
-        <v>0</v>
-      </c>
+      <c r="G519" t="inlineStr"/>
       <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -17504,6 +18663,9 @@
       <c r="H520" t="n">
         <v>3</v>
       </c>
+      <c r="I520" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -17538,6 +18700,9 @@
       <c r="H521" t="n">
         <v>3</v>
       </c>
+      <c r="I521" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -17572,6 +18737,9 @@
       <c r="H522" t="n">
         <v>4</v>
       </c>
+      <c r="I522" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -17606,6 +18774,9 @@
       <c r="H523" t="n">
         <v>3</v>
       </c>
+      <c r="I523" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -17640,6 +18811,9 @@
       <c r="H524" t="n">
         <v>3</v>
       </c>
+      <c r="I524" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -17674,6 +18848,9 @@
       <c r="H525" t="n">
         <v>2</v>
       </c>
+      <c r="I525" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -17708,6 +18885,9 @@
       <c r="H526" t="n">
         <v>2</v>
       </c>
+      <c r="I526" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -17742,6 +18922,9 @@
       <c r="H527" t="n">
         <v>4</v>
       </c>
+      <c r="I527" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -17774,6 +18957,9 @@
         <v>2</v>
       </c>
       <c r="H528" t="n">
+        <v>2</v>
+      </c>
+      <c r="I528" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17800,10 +18986,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G529" t="n">
-        <v>0</v>
-      </c>
+      <c r="G529" t="inlineStr"/>
       <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -17838,6 +19023,9 @@
       <c r="H530" t="n">
         <v>3</v>
       </c>
+      <c r="I530" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -17872,6 +19060,9 @@
       <c r="H531" t="n">
         <v>3</v>
       </c>
+      <c r="I531" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -17906,6 +19097,9 @@
       <c r="H532" t="n">
         <v>4</v>
       </c>
+      <c r="I532" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -17940,6 +19134,9 @@
       <c r="H533" t="n">
         <v>4</v>
       </c>
+      <c r="I533" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -17974,6 +19171,9 @@
       <c r="H534" t="n">
         <v>3</v>
       </c>
+      <c r="I534" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -18008,6 +19208,9 @@
       <c r="H535" t="n">
         <v>4</v>
       </c>
+      <c r="I535" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -18042,6 +19245,9 @@
       <c r="H536" t="n">
         <v>3</v>
       </c>
+      <c r="I536" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -18074,6 +19280,9 @@
         <v>4</v>
       </c>
       <c r="H537" t="n">
+        <v>4</v>
+      </c>
+      <c r="I537" t="n">
         <v>4</v>
       </c>
     </row>
@@ -18100,10 +19309,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G538" t="n">
-        <v>0</v>
-      </c>
+      <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -18138,6 +19346,9 @@
       <c r="H539" t="n">
         <v>2</v>
       </c>
+      <c r="I539" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -18172,6 +19383,9 @@
       <c r="H540" t="n">
         <v>3</v>
       </c>
+      <c r="I540" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -18206,6 +19420,9 @@
       <c r="H541" t="n">
         <v>3</v>
       </c>
+      <c r="I541" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -18240,6 +19457,9 @@
       <c r="H542" t="n">
         <v>2</v>
       </c>
+      <c r="I542" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -18272,6 +19492,9 @@
         <v>3</v>
       </c>
       <c r="H543" t="n">
+        <v>3</v>
+      </c>
+      <c r="I543" t="n">
         <v>3</v>
       </c>
     </row>
@@ -18298,10 +19521,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G544" t="n">
-        <v>0</v>
-      </c>
+      <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -18334,6 +19556,9 @@
         <v>2</v>
       </c>
       <c r="H545" t="n">
+        <v>2</v>
+      </c>
+      <c r="I545" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18360,10 +19585,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G546" t="n">
-        <v>0</v>
-      </c>
+      <c r="G546" t="inlineStr"/>
       <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -18398,6 +19622,9 @@
       <c r="H547" t="n">
         <v>3</v>
       </c>
+      <c r="I547" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -18432,6 +19659,9 @@
       <c r="H548" t="n">
         <v>2</v>
       </c>
+      <c r="I548" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -18466,6 +19696,9 @@
       <c r="H549" t="n">
         <v>3</v>
       </c>
+      <c r="I549" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -18500,6 +19733,9 @@
       <c r="H550" t="n">
         <v>3</v>
       </c>
+      <c r="I550" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -18532,6 +19768,9 @@
         <v>2</v>
       </c>
       <c r="H551" t="n">
+        <v>2</v>
+      </c>
+      <c r="I551" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18558,10 +19797,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G552" t="n">
-        <v>0</v>
-      </c>
+      <c r="G552" t="inlineStr"/>
       <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -18586,10 +19824,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G553" t="n">
-        <v>0</v>
-      </c>
+      <c r="G553" t="inlineStr"/>
       <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -18614,10 +19851,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G554" t="n">
-        <v>0</v>
-      </c>
+      <c r="G554" t="inlineStr"/>
       <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -18642,10 +19878,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G555" t="n">
-        <v>0</v>
-      </c>
+      <c r="G555" t="inlineStr"/>
       <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -18680,6 +19915,9 @@
       <c r="H556" t="n">
         <v>3</v>
       </c>
+      <c r="I556" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -18712,6 +19950,9 @@
         <v>3</v>
       </c>
       <c r="H557" t="n">
+        <v>3</v>
+      </c>
+      <c r="I557" t="n">
         <v>3</v>
       </c>
     </row>
@@ -18738,10 +19979,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G558" t="n">
-        <v>0</v>
-      </c>
+      <c r="G558" t="inlineStr"/>
       <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -18776,6 +20016,9 @@
       <c r="H559" t="n">
         <v>2</v>
       </c>
+      <c r="I559" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -18808,6 +20051,9 @@
         <v>2</v>
       </c>
       <c r="H560" t="n">
+        <v>2</v>
+      </c>
+      <c r="I560" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18834,10 +20080,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G561" t="n">
-        <v>0</v>
-      </c>
+      <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -18872,6 +20117,9 @@
       <c r="H562" t="n">
         <v>4</v>
       </c>
+      <c r="I562" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -18906,6 +20154,9 @@
       <c r="H563" t="n">
         <v>1</v>
       </c>
+      <c r="I563" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -18940,6 +20191,9 @@
       <c r="H564" t="n">
         <v>2</v>
       </c>
+      <c r="I564" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -18972,6 +20226,9 @@
         <v>3</v>
       </c>
       <c r="H565" t="n">
+        <v>3</v>
+      </c>
+      <c r="I565" t="n">
         <v>3</v>
       </c>
     </row>
@@ -18998,10 +20255,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G566" t="n">
-        <v>0</v>
-      </c>
+      <c r="G566" t="inlineStr"/>
       <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -19036,6 +20292,9 @@
       <c r="H567" t="n">
         <v>3</v>
       </c>
+      <c r="I567" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -19068,6 +20327,9 @@
         <v>2</v>
       </c>
       <c r="H568" t="n">
+        <v>2</v>
+      </c>
+      <c r="I568" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19094,10 +20356,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G569" t="n">
-        <v>0</v>
-      </c>
+      <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -19132,6 +20393,9 @@
       <c r="H570" t="n">
         <v>2</v>
       </c>
+      <c r="I570" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -19166,6 +20430,9 @@
       <c r="H571" t="n">
         <v>4</v>
       </c>
+      <c r="I571" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -19198,6 +20465,9 @@
         <v>3</v>
       </c>
       <c r="H572" t="n">
+        <v>3</v>
+      </c>
+      <c r="I572" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19224,10 +20494,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G573" t="n">
-        <v>0</v>
-      </c>
+      <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -19262,6 +20531,9 @@
       <c r="H574" t="n">
         <v>3</v>
       </c>
+      <c r="I574" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -19294,6 +20566,9 @@
         <v>3</v>
       </c>
       <c r="H575" t="n">
+        <v>3</v>
+      </c>
+      <c r="I575" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19320,10 +20595,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G576" t="n">
-        <v>0</v>
-      </c>
+      <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -19356,6 +20630,9 @@
         <v>2</v>
       </c>
       <c r="H577" t="n">
+        <v>2</v>
+      </c>
+      <c r="I577" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19382,10 +20659,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G578" t="n">
-        <v>0</v>
-      </c>
+      <c r="G578" t="inlineStr"/>
       <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -19420,6 +20696,9 @@
       <c r="H579" t="n">
         <v>2</v>
       </c>
+      <c r="I579" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -19454,6 +20733,9 @@
       <c r="H580" t="n">
         <v>2</v>
       </c>
+      <c r="I580" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -19488,6 +20770,9 @@
       <c r="H581" t="n">
         <v>2</v>
       </c>
+      <c r="I581" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -19522,6 +20807,9 @@
       <c r="H582" t="n">
         <v>2</v>
       </c>
+      <c r="I582" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -19556,6 +20844,9 @@
       <c r="H583" t="n">
         <v>3</v>
       </c>
+      <c r="I583" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -19590,6 +20881,9 @@
       <c r="H584" t="n">
         <v>3</v>
       </c>
+      <c r="I584" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -19624,6 +20918,9 @@
       <c r="H585" t="n">
         <v>2</v>
       </c>
+      <c r="I585" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -19656,6 +20953,9 @@
         <v>3</v>
       </c>
       <c r="H586" t="n">
+        <v>3</v>
+      </c>
+      <c r="I586" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19682,10 +20982,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G587" t="n">
-        <v>0</v>
-      </c>
+      <c r="G587" t="inlineStr"/>
       <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -19710,10 +21009,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G588" t="n">
-        <v>0</v>
-      </c>
+      <c r="G588" t="inlineStr"/>
       <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -19738,10 +21036,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G589" t="n">
-        <v>0</v>
-      </c>
+      <c r="G589" t="inlineStr"/>
       <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -19776,6 +21073,9 @@
       <c r="H590" t="n">
         <v>2</v>
       </c>
+      <c r="I590" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -19810,6 +21110,9 @@
       <c r="H591" t="n">
         <v>4</v>
       </c>
+      <c r="I591" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -19844,6 +21147,9 @@
       <c r="H592" t="n">
         <v>3</v>
       </c>
+      <c r="I592" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -19878,6 +21184,9 @@
       <c r="H593" t="n">
         <v>3</v>
       </c>
+      <c r="I593" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -19912,6 +21221,9 @@
       <c r="H594" t="n">
         <v>2</v>
       </c>
+      <c r="I594" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -19946,6 +21258,9 @@
       <c r="H595" t="n">
         <v>3</v>
       </c>
+      <c r="I595" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -19980,6 +21295,9 @@
       <c r="H596" t="n">
         <v>3</v>
       </c>
+      <c r="I596" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -20014,6 +21332,9 @@
       <c r="H597" t="n">
         <v>3</v>
       </c>
+      <c r="I597" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -20046,6 +21367,9 @@
         <v>3</v>
       </c>
       <c r="H598" t="n">
+        <v>3</v>
+      </c>
+      <c r="I598" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20072,10 +21396,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G599" t="n">
-        <v>0</v>
-      </c>
+      <c r="G599" t="inlineStr"/>
       <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -20110,6 +21433,9 @@
       <c r="H600" t="n">
         <v>3</v>
       </c>
+      <c r="I600" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -20144,6 +21470,9 @@
       <c r="H601" t="n">
         <v>4</v>
       </c>
+      <c r="I601" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -20178,6 +21507,9 @@
       <c r="H602" t="n">
         <v>4</v>
       </c>
+      <c r="I602" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -20212,6 +21544,9 @@
       <c r="H603" t="n">
         <v>4</v>
       </c>
+      <c r="I603" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -20246,6 +21581,9 @@
       <c r="H604" t="n">
         <v>3</v>
       </c>
+      <c r="I604" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -20280,6 +21618,9 @@
       <c r="H605" t="n">
         <v>4</v>
       </c>
+      <c r="I605" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -20314,6 +21655,9 @@
       <c r="H606" t="n">
         <v>4</v>
       </c>
+      <c r="I606" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -20348,6 +21692,9 @@
       <c r="H607" t="n">
         <v>4</v>
       </c>
+      <c r="I607" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -20382,6 +21729,9 @@
       <c r="H608" t="n">
         <v>4</v>
       </c>
+      <c r="I608" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -20416,6 +21766,9 @@
       <c r="H609" t="n">
         <v>4</v>
       </c>
+      <c r="I609" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -20450,6 +21803,9 @@
       <c r="H610" t="n">
         <v>4</v>
       </c>
+      <c r="I610" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -20484,6 +21840,9 @@
       <c r="H611" t="n">
         <v>3</v>
       </c>
+      <c r="I611" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -20518,6 +21877,9 @@
       <c r="H612" t="n">
         <v>3</v>
       </c>
+      <c r="I612" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -20552,6 +21914,9 @@
       <c r="H613" t="n">
         <v>3</v>
       </c>
+      <c r="I613" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -20586,6 +21951,9 @@
       <c r="H614" t="n">
         <v>3</v>
       </c>
+      <c r="I614" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -20620,6 +21988,9 @@
       <c r="H615" t="n">
         <v>4</v>
       </c>
+      <c r="I615" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -20654,6 +22025,9 @@
       <c r="H616" t="n">
         <v>4</v>
       </c>
+      <c r="I616" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -20686,6 +22060,9 @@
         <v>2</v>
       </c>
       <c r="H617" t="n">
+        <v>2</v>
+      </c>
+      <c r="I617" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20712,10 +22089,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G618" t="n">
-        <v>0</v>
-      </c>
+      <c r="G618" t="inlineStr"/>
       <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -20740,10 +22116,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G619" t="n">
-        <v>0</v>
-      </c>
+      <c r="G619" t="inlineStr"/>
       <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -20778,6 +22153,9 @@
       <c r="H620" t="n">
         <v>2</v>
       </c>
+      <c r="I620" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -20812,6 +22190,9 @@
       <c r="H621" t="n">
         <v>2</v>
       </c>
+      <c r="I621" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -20844,6 +22225,9 @@
         <v>3</v>
       </c>
       <c r="H622" t="n">
+        <v>3</v>
+      </c>
+      <c r="I622" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20870,10 +22254,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G623" t="n">
-        <v>0</v>
-      </c>
+      <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr"/>
+      <c r="I623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -20898,10 +22281,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G624" t="n">
-        <v>0</v>
-      </c>
+      <c r="G624" t="inlineStr"/>
       <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -20934,6 +22316,9 @@
         <v>3</v>
       </c>
       <c r="H625" t="n">
+        <v>3</v>
+      </c>
+      <c r="I625" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20960,10 +22345,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G626" t="n">
-        <v>0</v>
-      </c>
+      <c r="G626" t="inlineStr"/>
       <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -20998,6 +22382,9 @@
       <c r="H627" t="n">
         <v>4</v>
       </c>
+      <c r="I627" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -21032,6 +22419,9 @@
       <c r="H628" t="n">
         <v>3</v>
       </c>
+      <c r="I628" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -21064,6 +22454,9 @@
         <v>2</v>
       </c>
       <c r="H629" t="n">
+        <v>2</v>
+      </c>
+      <c r="I629" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21090,10 +22483,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G630" t="n">
-        <v>0</v>
-      </c>
+      <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -21126,6 +22518,9 @@
         <v>3</v>
       </c>
       <c r="H631" t="n">
+        <v>3</v>
+      </c>
+      <c r="I631" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21152,10 +22547,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G632" t="n">
-        <v>0</v>
-      </c>
+      <c r="G632" t="inlineStr"/>
       <c r="H632" t="inlineStr"/>
+      <c r="I632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -21180,10 +22574,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G633" t="n">
-        <v>0</v>
-      </c>
+      <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr"/>
+      <c r="I633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -21208,10 +22601,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G634" t="n">
-        <v>0</v>
-      </c>
+      <c r="G634" t="inlineStr"/>
       <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -21244,6 +22636,9 @@
         <v>3</v>
       </c>
       <c r="H635" t="n">
+        <v>3</v>
+      </c>
+      <c r="I635" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21270,10 +22665,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G636" t="n">
-        <v>0</v>
-      </c>
+      <c r="G636" t="inlineStr"/>
       <c r="H636" t="inlineStr"/>
+      <c r="I636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -21306,6 +22700,9 @@
         <v>2</v>
       </c>
       <c r="H637" t="n">
+        <v>2</v>
+      </c>
+      <c r="I637" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21332,10 +22729,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G638" t="n">
-        <v>0</v>
-      </c>
+      <c r="G638" t="inlineStr"/>
       <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -21370,6 +22766,9 @@
       <c r="H639" t="n">
         <v>2</v>
       </c>
+      <c r="I639" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -21404,6 +22803,9 @@
       <c r="H640" t="n">
         <v>4</v>
       </c>
+      <c r="I640" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -21438,6 +22840,9 @@
       <c r="H641" t="n">
         <v>4</v>
       </c>
+      <c r="I641" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -21472,6 +22877,9 @@
       <c r="H642" t="n">
         <v>3</v>
       </c>
+      <c r="I642" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -21506,6 +22914,9 @@
       <c r="H643" t="n">
         <v>3</v>
       </c>
+      <c r="I643" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -21540,6 +22951,9 @@
       <c r="H644" t="n">
         <v>2</v>
       </c>
+      <c r="I644" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -21574,6 +22988,9 @@
       <c r="H645" t="n">
         <v>2</v>
       </c>
+      <c r="I645" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -21608,6 +23025,9 @@
       <c r="H646" t="n">
         <v>3</v>
       </c>
+      <c r="I646" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -21642,6 +23062,9 @@
       <c r="H647" t="n">
         <v>3</v>
       </c>
+      <c r="I647" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -21676,6 +23099,9 @@
       <c r="H648" t="n">
         <v>4</v>
       </c>
+      <c r="I648" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -21710,6 +23136,9 @@
       <c r="H649" t="n">
         <v>3</v>
       </c>
+      <c r="I649" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -21742,6 +23171,9 @@
         <v>3</v>
       </c>
       <c r="H650" t="n">
+        <v>3</v>
+      </c>
+      <c r="I650" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21768,10 +23200,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G651" t="n">
-        <v>0</v>
-      </c>
+      <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -21804,6 +23235,9 @@
         <v>2</v>
       </c>
       <c r="H652" t="n">
+        <v>2</v>
+      </c>
+      <c r="I652" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21830,10 +23264,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G653" t="n">
-        <v>0</v>
-      </c>
+      <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -21866,6 +23299,9 @@
         <v>2</v>
       </c>
       <c r="H654" t="n">
+        <v>2</v>
+      </c>
+      <c r="I654" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21892,10 +23328,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G655" t="n">
-        <v>0</v>
-      </c>
+      <c r="G655" t="inlineStr"/>
       <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -21930,6 +23365,9 @@
       <c r="H656" t="n">
         <v>2</v>
       </c>
+      <c r="I656" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -21964,6 +23402,9 @@
       <c r="H657" t="n">
         <v>3</v>
       </c>
+      <c r="I657" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -21996,6 +23437,9 @@
         <v>2</v>
       </c>
       <c r="H658" t="n">
+        <v>2</v>
+      </c>
+      <c r="I658" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22022,10 +23466,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G659" t="n">
-        <v>0</v>
-      </c>
+      <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -22060,6 +23503,9 @@
       <c r="H660" t="n">
         <v>2</v>
       </c>
+      <c r="I660" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -22094,6 +23540,9 @@
       <c r="H661" t="n">
         <v>3</v>
       </c>
+      <c r="I661" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -22126,6 +23575,9 @@
         <v>3</v>
       </c>
       <c r="H662" t="n">
+        <v>3</v>
+      </c>
+      <c r="I662" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22152,10 +23604,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G663" t="n">
-        <v>0</v>
-      </c>
+      <c r="G663" t="inlineStr"/>
       <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -22188,6 +23639,9 @@
         <v>3</v>
       </c>
       <c r="H664" t="n">
+        <v>3</v>
+      </c>
+      <c r="I664" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22214,10 +23668,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G665" t="n">
-        <v>0</v>
-      </c>
+      <c r="G665" t="inlineStr"/>
       <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -22252,6 +23705,9 @@
       <c r="H666" t="n">
         <v>3</v>
       </c>
+      <c r="I666" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -22286,6 +23742,9 @@
       <c r="H667" t="n">
         <v>3</v>
       </c>
+      <c r="I667" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -22320,6 +23779,9 @@
       <c r="H668" t="n">
         <v>3</v>
       </c>
+      <c r="I668" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -22354,6 +23816,9 @@
       <c r="H669" t="n">
         <v>2</v>
       </c>
+      <c r="I669" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -22388,6 +23853,9 @@
       <c r="H670" t="n">
         <v>3</v>
       </c>
+      <c r="I670" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -22422,6 +23890,9 @@
       <c r="H671" t="n">
         <v>2</v>
       </c>
+      <c r="I671" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -22456,6 +23927,9 @@
       <c r="H672" t="n">
         <v>2</v>
       </c>
+      <c r="I672" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -22490,6 +23964,9 @@
       <c r="H673" t="n">
         <v>4</v>
       </c>
+      <c r="I673" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -22524,6 +24001,9 @@
       <c r="H674" t="n">
         <v>4</v>
       </c>
+      <c r="I674" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -22558,6 +24038,9 @@
       <c r="H675" t="n">
         <v>3</v>
       </c>
+      <c r="I675" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -22592,6 +24075,9 @@
       <c r="H676" t="n">
         <v>3</v>
       </c>
+      <c r="I676" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -22626,6 +24112,9 @@
       <c r="H677" t="n">
         <v>4</v>
       </c>
+      <c r="I677" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -22660,6 +24149,9 @@
       <c r="H678" t="n">
         <v>4</v>
       </c>
+      <c r="I678" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -22694,6 +24186,9 @@
       <c r="H679" t="n">
         <v>3</v>
       </c>
+      <c r="I679" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -22728,6 +24223,9 @@
       <c r="H680" t="n">
         <v>3</v>
       </c>
+      <c r="I680" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -22762,6 +24260,9 @@
       <c r="H681" t="n">
         <v>4</v>
       </c>
+      <c r="I681" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -22796,6 +24297,9 @@
       <c r="H682" t="n">
         <v>2</v>
       </c>
+      <c r="I682" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -22828,6 +24332,9 @@
         <v>3</v>
       </c>
       <c r="H683" t="n">
+        <v>3</v>
+      </c>
+      <c r="I683" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22854,10 +24361,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G684" t="n">
-        <v>0</v>
-      </c>
+      <c r="G684" t="inlineStr"/>
       <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -22890,6 +24396,9 @@
         <v>2</v>
       </c>
       <c r="H685" t="n">
+        <v>2</v>
+      </c>
+      <c r="I685" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22916,10 +24425,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G686" t="n">
-        <v>0</v>
-      </c>
+      <c r="G686" t="inlineStr"/>
       <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -22954,6 +24462,9 @@
       <c r="H687" t="n">
         <v>2</v>
       </c>
+      <c r="I687" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -22988,6 +24499,9 @@
       <c r="H688" t="n">
         <v>3</v>
       </c>
+      <c r="I688" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -23022,6 +24536,9 @@
       <c r="H689" t="n">
         <v>3</v>
       </c>
+      <c r="I689" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -23056,6 +24573,9 @@
       <c r="H690" t="n">
         <v>3</v>
       </c>
+      <c r="I690" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -23088,6 +24608,9 @@
         <v>4</v>
       </c>
       <c r="H691" t="n">
+        <v>4</v>
+      </c>
+      <c r="I691" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23114,10 +24637,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G692" t="n">
-        <v>0</v>
-      </c>
+      <c r="G692" t="inlineStr"/>
       <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -23152,6 +24674,9 @@
       <c r="H693" t="n">
         <v>3</v>
       </c>
+      <c r="I693" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -23184,6 +24709,9 @@
         <v>3</v>
       </c>
       <c r="H694" t="n">
+        <v>3</v>
+      </c>
+      <c r="I694" t="n">
         <v>3</v>
       </c>
     </row>
@@ -23210,10 +24738,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G695" t="n">
-        <v>0</v>
-      </c>
+      <c r="G695" t="inlineStr"/>
       <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -23246,6 +24773,9 @@
         <v>3</v>
       </c>
       <c r="H696" t="n">
+        <v>3</v>
+      </c>
+      <c r="I696" t="n">
         <v>3</v>
       </c>
     </row>
@@ -23272,10 +24802,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G697" t="n">
-        <v>0</v>
-      </c>
+      <c r="G697" t="inlineStr"/>
       <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -23300,10 +24829,9 @@
           <t>Thiếu dữ liệu Level</t>
         </is>
       </c>
-      <c r="G698" t="n">
-        <v>0</v>
-      </c>
+      <c r="G698" t="inlineStr"/>
       <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -23338,6 +24866,9 @@
       <c r="H699" t="n">
         <v>2</v>
       </c>
+      <c r="I699" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -23372,6 +24903,9 @@
       <c r="H700" t="n">
         <v>3</v>
       </c>
+      <c r="I700" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -23404,6 +24938,9 @@
         <v>3</v>
       </c>
       <c r="H701" t="n">
+        <v>3</v>
+      </c>
+      <c r="I701" t="n">
         <v>3</v>
       </c>
     </row>
